--- a/public/templates/import_budget.xlsx
+++ b/public/templates/import_budget.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>perpost</t>
   </si>
@@ -77,47 +77,51 @@
     <t>2025</t>
   </si>
   <si>
-    <t>EVENT000001</t>
-  </si>
-  <si>
-    <t>EVENT000003</t>
-  </si>
-  <si>
-    <t>EVENT000002</t>
-  </si>
-  <si>
     <t>OTH000001</t>
   </si>
   <si>
-    <t>Event Chinese New Year</t>
-  </si>
-  <si>
-    <t>Event School Holiday &amp; JGS</t>
-  </si>
-  <si>
-    <t>Event Christmas &amp; Midnite Sale</t>
-  </si>
-  <si>
-    <t>Beban Promosi</t>
-  </si>
-  <si>
-    <t>Beban Lain Privilege</t>
-  </si>
-  <si>
     <t>62010400</t>
   </si>
   <si>
-    <t>62010300</t>
-  </si>
-  <si>
-    <t>62010100</t>
+    <t>activity_descr</t>
+  </si>
+  <si>
+    <t>qty_budget</t>
+  </si>
+  <si>
+    <t>unit_price_budget</t>
+  </si>
+  <si>
+    <t>Langganan Cloud GCP</t>
+  </si>
+  <si>
+    <t>Google Cloud</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Data Analyst Power BI</t>
+  </si>
+  <si>
+    <t>Maintenance Server</t>
+  </si>
+  <si>
+    <t>1 Tahun 4x</t>
+  </si>
+  <si>
+    <t>OTH000002</t>
+  </si>
+  <si>
+    <t>OTH000003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
@@ -157,10 +161,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -442,18 +448,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="29.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="1" customWidth="1"/>
+    <col min="8" max="19" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,293 +473,229 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="F2" s="2">
-        <v>100000000</v>
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="4">
+        <v>12</v>
       </c>
       <c r="G2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="H2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="J2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="K2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="L2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="M2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="N2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="O2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="P2" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="R2" s="2">
+        <v>10000000</v>
+      </c>
+      <c r="S2" s="2">
+        <v>10000000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="F3" s="2">
-        <v>100000000</v>
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>100000000</v>
+        <v>4000000</v>
       </c>
       <c r="H3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2">
-        <v>100000000</v>
+        <v>4000000</v>
       </c>
       <c r="L3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="O3" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="P3" s="2">
-        <v>100000000</v>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="F4" s="2">
-        <v>100000000</v>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="4">
+        <v>4</v>
       </c>
       <c r="G4" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="H4" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I4" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="L4" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="N4" s="2">
-        <v>100000000</v>
+        <v>0</v>
       </c>
       <c r="O4" s="2">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="P4" s="2">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="G5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="H5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="I5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="J5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="K5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="L5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="M5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="N5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="O5" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="P5" s="2">
-        <v>20000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="F6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="G6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="H6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="J6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="K6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="L6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="M6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="N6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="O6" s="2">
-        <v>30000000</v>
-      </c>
-      <c r="P6" s="2">
-        <v>30000000</v>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2">
+        <v>10000000</v>
       </c>
     </row>
   </sheetData>
